--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentPrdInfo_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentPrdInfo_export.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="委托销售产品编码" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>发行机构代码</t>
   </si>
@@ -44,10 +44,6 @@
   </si>
   <si>
     <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -441,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
@@ -455,7 +451,7 @@
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -477,11 +473,8 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B3" s="2"/>
     </row>
   </sheetData>
